--- a/reports/jobs_2026-09-26.xlsx
+++ b/reports/jobs_2026-09-26.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1092,12 +1092,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>RTL Design Engineer – Memory Controller</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1110,7 +1110,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/rtl-design-engineer-memory-controller/33099/100674776368</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1135,12 +1139,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1153,11 +1157,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1243,7 +1243,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Remote - India</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -1251,12 +1255,12 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1268,17 +1272,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1288,7 +1292,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1298,12 +1302,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1320,12 +1324,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1335,7 +1339,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1345,7 +1349,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1367,12 +1371,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1382,7 +1386,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru/Gurugram Full-time</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1392,7 +1396,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1414,7 +1418,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1429,7 +1433,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru/Gurugram Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1439,7 +1443,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1461,7 +1465,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1476,7 +1480,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1486,7 +1490,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1508,12 +1512,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1521,11 +1525,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1568,7 +1568,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -1576,7 +1580,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1598,7 +1602,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1623,7 +1627,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1645,7 +1649,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1670,7 +1674,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1692,7 +1696,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1717,7 +1721,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1739,12 +1743,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1764,7 +1768,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1781,17 +1785,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1801,7 +1805,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1811,12 +1815,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1833,7 +1837,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1858,7 +1862,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1880,7 +1884,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1905,7 +1909,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1922,17 +1926,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1940,11 +1944,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Engineering Leader, Google COE</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2012,17 +2012,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2060,12 +2060,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2098,17 +2098,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2116,7 +2116,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -2124,12 +2128,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2146,7 +2150,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2171,7 +2175,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2188,17 +2192,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2208,7 +2212,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2218,12 +2222,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2235,12 +2239,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2255,7 +2259,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2265,12 +2269,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2282,17 +2286,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2302,7 +2306,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2312,12 +2316,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2329,17 +2333,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2347,11 +2351,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2437,7 +2437,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -2445,12 +2449,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2467,7 +2471,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2482,7 +2486,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2492,7 +2496,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2509,12 +2513,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2527,11 +2531,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -2539,12 +2539,12 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2556,12 +2556,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2574,7 +2574,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -2582,12 +2586,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2604,7 +2608,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2629,7 +2633,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2646,17 +2650,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2664,11 +2668,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2693,17 +2693,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Intern - Talent Acquisition (Tech Hiring)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2754,7 +2754,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -2762,12 +2766,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2784,7 +2788,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition (Tech Hiring)</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2799,7 +2803,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2809,7 +2813,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2831,7 +2835,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2846,7 +2850,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2856,7 +2860,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2878,7 +2882,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2893,7 +2897,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2903,7 +2907,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2925,7 +2929,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Talent Acquisition Intern - Gurgaon</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2940,7 +2944,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2950,7 +2954,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2967,17 +2971,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Gurgaon</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2985,11 +2989,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, Haryana</t>
-        </is>
-      </c>
+      <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -2997,12 +2997,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3014,17 +3014,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3032,7 +3032,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -3040,12 +3044,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3062,12 +3066,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3087,7 +3091,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3109,12 +3113,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3134,7 +3138,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3151,17 +3155,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3169,11 +3173,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -3181,12 +3181,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3216,7 +3216,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -3224,12 +3228,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3246,12 +3250,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3261,7 +3265,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3271,7 +3275,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3293,12 +3297,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3308,7 +3312,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3318,7 +3322,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3340,12 +3344,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3355,7 +3359,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3365,7 +3369,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3387,12 +3391,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3402,7 +3406,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3412,7 +3416,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3429,17 +3433,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3449,7 +3453,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3459,12 +3463,12 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3476,17 +3480,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Sound Designer - AI</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3494,11 +3498,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3541,7 +3541,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -3549,12 +3553,12 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3571,12 +3575,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3596,7 +3600,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3613,17 +3617,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3631,11 +3635,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3678,7 +3678,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -3686,12 +3690,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3703,12 +3707,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Thoughtworks India</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Developer (Vapasi) - Intern</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3718,12 +3722,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1–5 years</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3733,12 +3737,12 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3750,27 +3754,27 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Developer (Vapasi) - Intern</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>1–5 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3780,12 +3784,12 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3802,12 +3806,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3827,7 +3831,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3841,55 +3845,8 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I75"/>
+  <autoFilter ref="A1:I74"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -3964,7 +3921,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3976,7 +3932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4084,15 +4040,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>ideaForge</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://ideaforgetech.com/careers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://ideaforgetech.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4101,18 +4077,38 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Capillary Technologies</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.capillarytech.com/careers/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4121,38 +4117,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Capillary Technologies</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.capillarytech.com/careers/</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Darwinbox</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://darwinbox.com/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4161,18 +4137,38 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4181,18 +4177,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4201,18 +4197,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4221,38 +4217,38 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OYO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.oyorooms.com/careers/</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pocket FM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://pocketfm.com/careers</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+  - navigating to "https://pocketfm.com/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4261,38 +4257,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Pocket FM</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://pocketfm.com/careers</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://pocketfm.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4301,18 +4277,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4321,18 +4297,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
